--- a/artfynd/A 12818-2024 artfynd.xlsx
+++ b/artfynd/A 12818-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117894244</v>
+        <v>117894243</v>
       </c>
       <c r="B2" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449123</v>
+        <v>449098</v>
       </c>
       <c r="R2" t="n">
-        <v>7092563</v>
+        <v>7092695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117894243</v>
+        <v>117894244</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449098</v>
+        <v>449123</v>
       </c>
       <c r="R3" t="n">
-        <v>7092695</v>
+        <v>7092563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
